--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0229.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0229.xlsx
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Complete Time {0}</t>
+          <t>Thời Gian Hoàn Thành {0}</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Complete Time {0}</t>
+          <t>Thời Gian Hoàn Thành {0}</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiều lượt luyện bắn trong thời gian giới hạn.</t>
+          <t>Hoàn thành nhiều lượt bắn trong thời gian giới hạn.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Bạn đã thêm {0} vào danh sách chặn</t>
+          <t>Bạn đã thêm {0} vào danh sách chặn.</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Bạn không thể tìm chính mình.</t>
+          <t>Bạn không thể tìm kiếm chính mình.</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Đã chuyển sang chạy ({Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để chuyển đổi)</t>
+          <t>Đã chuyển sang chạy ({Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để chuyển đổi)</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Đã chuyển sang đi bộ ({Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để chuyển đổi)</t>
+          <t>Đã chuyển sang đi bộ ({Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để chuyển đổi)</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Bạn đã thành thạo chế tác {0}.</t>
+          <t>Bạn đã thành thạo chế tạo {0}.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Bạn có thể đổi thưởng ngay bây giờ.</t>
+          <t>Bạn có thể đổi phần thưởng ngay bây giờ.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Không thể nhận thưởng từ thư đã hết hạn.</t>
+          <t>Không thể nhận phần thưởng từ thư đã hết hạn.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Bạn đã xóa {0} khỏi danh sách chặn</t>
+          <t>Bạn đã xóa {0} khỏi danh sách chặn.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Character Locked {0}</t>
+          <t>Đã khóa nhân vật {0}</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Ảnh đã lưu vào thư mục /{0}</t>
+          <t>Ảnh đã được lưu vào thư mục /{0}</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Bạn đã được thêm vào danh sách chặn của người chơi này.</t>
+          <t>Bạn đã bị thêm vào danh sách chặn của người chơi này.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>{0}/&lt;color=#808080&gt;{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Một Rover không nhớ quá khứ.</t>
+          <t>Một Vận Mệnh Giả không nhớ quá khứ.</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Hãy chọn một Banner cho Chosen Triệu Tập trước đã.</t>
+          <t>Hãy chọn một Banner cho Chosen Convene trước đã.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Chọn cái này?</t>
+          <t>Chọn mục này?</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Bạn sẽ không thể thay đổi ngoại hình Rover trong vòng 24 giờ nữa.</t>
+          <t>Bạn sẽ không thể thay đổi ngoại hình của Rover trong vòng 24 giờ nữa.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>{0}&lt;color=#a1a1a1&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể đặt {0} Cộng Hưởng Giả.</t>
+          <t>Bạn chỉ có thể đặt {0} Resonator.</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>&lt;color=#ff0000ff&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>&lt;\color=#ffd12f&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>&lt;color=#c25757&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>&lt;color=#ffffff&gt;Lv. {0}/&lt;/color&gt;&lt;color=#c1c1c1&gt;{1}&lt;/color&gt;</t>
+          <t>&lt;color=#ffffff&gt;Cấp {0}/&lt;/color&gt;&lt;color=#c1c1c1&gt;{1}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25408,7 +25408,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>&lt;color=#ac8549&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -26645,7 +26645,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Đội hiện tại không có Cộng Hưởng Giả</t>
+          <t>Đội hiện tại không có Resonator</t>
         </is>
       </c>
     </row>
@@ -30480,7 +30480,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>&lt;color=#bca868&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -31065,7 +31065,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>&lt;color=#c7fe96&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -32040,7 +32040,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Nhân Vật Thử Nghiệm sẽ không hiển thị trong giao diện Cộng Hưởng Giả.</t>
+          <t>Nhân Vật Thử Nghiệm sẽ không hiển thị trong giao diện Resonator.</t>
         </is>
       </c>
     </row>
